--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Collegetown_20251114.xlsx
@@ -450,20 +450,14 @@
           <t>Mop Head Cut (White)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -473,20 +467,14 @@
           <t>Container - Soup (32oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -500,20 +488,14 @@
           <t>Container - Soup (16oz)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.22</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15.66</v>
       </c>
     </row>
     <row r="5">
@@ -527,20 +509,14 @@
           <t>Container - Soup (8oz)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4.11</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20.55</v>
       </c>
     </row>
     <row r="6">
@@ -550,20 +526,14 @@
           <t>Lid - Soup (6/16 oz)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.28</v>
       </c>
     </row>
     <row r="7">
@@ -577,20 +547,14 @@
           <t>Jam - Strawberry</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -604,20 +568,14 @@
           <t>Wrap - Foil (9" x 10.75")</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -631,20 +589,14 @@
           <t>Wrap - Paper (15" x 10.75")</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.97</v>
       </c>
     </row>
     <row r="10">
@@ -658,20 +610,14 @@
           <t>Cup - Portion (3.25oz)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5.23</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>5.23</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.23</v>
       </c>
     </row>
     <row r="11">
@@ -685,20 +631,14 @@
           <t>Lid - Portion (3.25oz)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>8.43</t>
-        </is>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.43</v>
       </c>
     </row>
     <row r="12">
@@ -712,20 +652,14 @@
           <t>Lid - Portion (2oz)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.47</v>
       </c>
     </row>
     <row r="13">
@@ -739,20 +673,14 @@
           <t>Wrap - Paper (6" x 10.75")</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.82</v>
       </c>
     </row>
     <row r="14">
@@ -762,20 +690,14 @@
           <t>Bag - Wax (Sandwich)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>21.01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="E14" t="n">
+        <v>42.02</v>
       </c>
     </row>
     <row r="15">
@@ -785,20 +707,14 @@
           <t>Register Tape - Thermal (3.125" x 230')</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>49.99</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>49.99</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="E15" t="n">
+        <v>49.99</v>
       </c>
     </row>
     <row r="16">
@@ -808,20 +724,14 @@
           <t>Tea Bags - Lemon Ginger (Twinings)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.83</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>11.49</t>
-        </is>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.49</v>
       </c>
     </row>
     <row r="17">
@@ -831,20 +741,14 @@
           <t>Tea Bags - Pomegrantate &amp; Rasp (Twinings)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>6.96</t>
-        </is>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6.96</v>
       </c>
     </row>
     <row r="18">
@@ -854,20 +758,14 @@
           <t>Iced Tea - Green Citrus Ginko</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>70.40</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>70.40</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -877,20 +775,14 @@
           <t>Hazelnut Coffee (Grounded, Bulk)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>38.00</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>76.00</t>
-        </is>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>38</v>
+      </c>
+      <c r="E19" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -904,20 +796,14 @@
           <t>Degreaser - for Panini Press (Dawn)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>41.16</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>41.16</t>
-        </is>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41.16</v>
       </c>
     </row>
     <row r="21">
@@ -931,20 +817,14 @@
           <t>Matcha - Jade Leaf</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>44.07</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>88.14</t>
-        </is>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>88.14</v>
       </c>
     </row>
     <row r="22">
@@ -958,20 +838,14 @@
           <t>Torani - Caramel Sauce</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -985,20 +859,14 @@
           <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1012,20 +880,14 @@
           <t>White Hot Chocolate - Ghirardelli</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>47.16</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>47.16</t>
-        </is>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="E24" t="n">
+        <v>47.16</v>
       </c>
     </row>
     <row r="25">
@@ -1035,20 +897,14 @@
           <t>Hot Chocolate (Bulk)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1062,20 +918,14 @@
           <t>Flax Seeds</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.58</v>
       </c>
     </row>
     <row r="27">
@@ -1089,20 +939,14 @@
           <t>Smoked Salmon (Sliced)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>85.85</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>515.10</t>
-        </is>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>515.1</v>
       </c>
     </row>
     <row r="28">
@@ -1116,20 +960,14 @@
           <t>Kilogram Chai Concentrate</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>86.10</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>344.40</t>
-        </is>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>344.4</v>
       </c>
     </row>
     <row r="29">
@@ -1143,20 +981,14 @@
           <t>Container - Deli (16oz)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>19.11</t>
-        </is>
+      <c r="C29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19.11</v>
       </c>
     </row>
     <row r="30">
@@ -1170,20 +1002,14 @@
           <t>Lid - Deli (6/32oz)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8.15</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1023,14 @@
           <t>Scrubbies - Steel</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8.09</v>
       </c>
     </row>
     <row r="32">
@@ -1224,20 +1044,14 @@
           <t>FRZ Fruit - Mango</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>51.43</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>154.29</t>
-        </is>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="E32" t="n">
+        <v>154.29</v>
       </c>
     </row>
     <row r="33">
@@ -1251,20 +1065,14 @@
           <t>Bindi - Cake Tiramisu Round</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>32.79</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>32.79</t>
-        </is>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="E33" t="n">
+        <v>32.79</v>
       </c>
     </row>
     <row r="34">
@@ -1278,20 +1086,14 @@
           <t>Sweet Street - Chocolate Lovin</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>45.50</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>45.50</t>
-        </is>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>45.5</v>
       </c>
     </row>
     <row r="35">
@@ -1305,20 +1107,14 @@
           <t>Grandma's Coffee Cake - Apple</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="E35" t="n">
+        <v>18.35</v>
       </c>
     </row>
     <row r="36">
@@ -1332,20 +1128,14 @@
           <t>Smoked Salmon (Retail Pack)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>79.83</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>159.66</t>
-        </is>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>79.83</v>
+      </c>
+      <c r="E36" t="n">
+        <v>159.66</v>
       </c>
     </row>
     <row r="37">
@@ -1359,20 +1149,14 @@
           <t>Whitefish Salad</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>77.97</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>77.97</t>
-        </is>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="E37" t="n">
+        <v>77.97</v>
       </c>
     </row>
     <row r="38">
@@ -1386,20 +1170,14 @@
           <t>Chobani - Drinkable Yogurt</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>17.99</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>35.98</t>
-        </is>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="E38" t="n">
+        <v>35.98</v>
       </c>
     </row>
   </sheetData>
